--- a/minio/minio_data/Workshop/Warehouse/Installation/ES755-A2501-MD1.xlsx
+++ b/minio/minio_data/Workshop/Warehouse/Installation/ES755-A2501-MD1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="28800" windowHeight="13260"/>
   </bookViews>
   <sheets>
     <sheet name="Parts List" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -815,12 +815,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1126,43 +1120,43 @@
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1">
@@ -1549,15 +1543,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.5740740740741" customWidth="1"/>
-    <col min="3" max="3" width="20.712962962963" customWidth="1"/>
-    <col min="4" max="4" width="36.1388888888889" customWidth="1"/>
-    <col min="5" max="5" width="12.1388888888889" customWidth="1"/>
-    <col min="6" max="6" width="50.287037037037" customWidth="1"/>
-    <col min="7" max="8" width="22.4259259259259" customWidth="1"/>
-    <col min="9" max="9" width="20.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="23.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="36.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="12.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
+    <col min="7" max="8" width="22.4285714285714" customWidth="1"/>
+    <col min="9" max="9" width="20.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
@@ -1589,7 +1583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="43.2" spans="1:9">
+    <row r="2" ht="45" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1611,12 +1605,15 @@
       <c r="G2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10"/>
+      <c r="H2" s="10" t="str">
+        <f ca="1">CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)</f>
+        <v>S8T3H3</v>
+      </c>
       <c r="I2" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="43.2" spans="1:9">
+    <row r="3" ht="45" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -1638,12 +1635,15 @@
       <c r="G3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="10"/>
+      <c r="H3" s="10" t="str">
+        <f ca="1" t="shared" ref="H3:H12" si="0">CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)</f>
+        <v>V0P5N5</v>
+      </c>
       <c r="I3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="43.2" spans="1:9">
+    <row r="4" ht="45" spans="1:9">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -1665,12 +1665,15 @@
       <c r="G4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="10"/>
+      <c r="H4" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>C2O9U9</v>
+      </c>
       <c r="I4" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="43.2" spans="1:9">
+    <row r="5" ht="45" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -1692,12 +1695,15 @@
       <c r="G5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="10"/>
+      <c r="H5" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>R9W4X6</v>
+      </c>
       <c r="I5" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="43.2" spans="1:9">
+    <row r="6" ht="45" spans="1:9">
       <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
@@ -1719,12 +1725,15 @@
       <c r="G6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>Z7K9M4</v>
+      </c>
       <c r="I6" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="43.2" spans="1:9">
+    <row r="7" ht="45" spans="1:9">
       <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
@@ -1746,12 +1755,15 @@
       <c r="G7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="10"/>
+      <c r="H7" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>V3P0A9</v>
+      </c>
       <c r="I7" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" ht="43.2" spans="1:9">
+    <row r="8" ht="45" spans="1:9">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -1773,12 +1785,15 @@
       <c r="G8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>K5E1V7</v>
+      </c>
       <c r="I8" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" ht="57.6" spans="1:9">
+    <row r="9" ht="60" spans="1:9">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -1800,12 +1815,15 @@
       <c r="G9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="10"/>
+      <c r="H9" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>F6S5W3</v>
+      </c>
       <c r="I9" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" ht="43.2" spans="1:9">
+    <row r="10" ht="45" spans="1:9">
       <c r="A10" s="3" t="s">
         <v>43</v>
       </c>
@@ -1827,12 +1845,15 @@
       <c r="G10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>Y2W8D5</v>
+      </c>
       <c r="I10" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:9">
+    <row r="11" ht="45" spans="1:9">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -1854,12 +1875,15 @@
       <c r="G11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="10"/>
+      <c r="H11" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>P3X6I9</v>
+      </c>
       <c r="I11" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" ht="43.2" spans="1:9">
+    <row r="12" ht="45" spans="1:9">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -1881,12 +1905,15 @@
       <c r="G12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="10"/>
+      <c r="H12" s="10" t="str">
+        <f ca="1" t="shared" si="0"/>
+        <v>H0D4I5</v>
+      </c>
       <c r="I12" s="11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" ht="43.2" spans="1:9">
+    <row r="13" ht="45" spans="1:9">
       <c r="A13" s="3" t="s">
         <v>52</v>
       </c>
@@ -1908,12 +1935,15 @@
       <c r="G13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="10"/>
+      <c r="H13" s="10" t="str">
+        <f ca="1" t="shared" ref="H13:H22" si="1">CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)</f>
+        <v>S2O4T6</v>
+      </c>
       <c r="I13" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" ht="43.2" spans="1:9">
+    <row r="14" ht="45" spans="1:9">
       <c r="A14" s="3" t="s">
         <v>57</v>
       </c>
@@ -1935,12 +1965,15 @@
       <c r="G14" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>V3V7Y9</v>
+      </c>
       <c r="I14" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="43.2" spans="1:9">
+    <row r="15" ht="45" spans="1:9">
       <c r="A15" s="3" t="s">
         <v>61</v>
       </c>
@@ -1962,12 +1995,15 @@
       <c r="G15" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="10"/>
+      <c r="H15" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>F4Z7X2</v>
+      </c>
       <c r="I15" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="43.2" spans="1:9">
+    <row r="16" ht="60" spans="1:9">
       <c r="A16" s="3" t="s">
         <v>65</v>
       </c>
@@ -1989,12 +2025,15 @@
       <c r="G16" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="10"/>
+      <c r="H16" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>P4I0G8</v>
+      </c>
       <c r="I16" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="43.2" spans="1:9">
+    <row r="17" ht="45" spans="1:9">
       <c r="A17" s="3" t="s">
         <v>69</v>
       </c>
@@ -2016,12 +2055,15 @@
       <c r="G17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>U9H9C8</v>
+      </c>
       <c r="I17" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" ht="43.2" spans="1:9">
+    <row r="18" ht="45" spans="1:9">
       <c r="A18" s="3" t="s">
         <v>74</v>
       </c>
@@ -2043,12 +2085,15 @@
       <c r="G18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="10"/>
+      <c r="H18" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>N5M9V9</v>
+      </c>
       <c r="I18" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" ht="43.2" spans="1:9">
+    <row r="19" ht="45" spans="1:9">
       <c r="A19" s="3" t="s">
         <v>78</v>
       </c>
@@ -2070,12 +2115,15 @@
       <c r="G19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H19" s="10"/>
+      <c r="H19" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>Y5J5R3</v>
+      </c>
       <c r="I19" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="43.2" spans="1:9">
+    <row r="20" ht="60" spans="1:9">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -2097,12 +2145,15 @@
       <c r="G20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H20" s="10"/>
+      <c r="H20" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>H8R2E8</v>
+      </c>
       <c r="I20" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" ht="43.2" spans="1:9">
+    <row r="21" ht="45" spans="1:9">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -2124,12 +2175,15 @@
       <c r="G21" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>J8Q5I6</v>
+      </c>
       <c r="I21" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="57.6" spans="1:9">
+    <row r="22" ht="60" spans="1:9">
       <c r="A22" s="3" t="s">
         <v>88</v>
       </c>
@@ -2151,12 +2205,15 @@
       <c r="G22" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="10"/>
+      <c r="H22" s="10" t="str">
+        <f ca="1" t="shared" si="1"/>
+        <v>A5M9C9</v>
+      </c>
       <c r="I22" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" ht="43.2" spans="1:9">
+    <row r="23" ht="45" spans="1:9">
       <c r="A23" s="3" t="s">
         <v>92</v>
       </c>
@@ -2178,12 +2235,15 @@
       <c r="G23" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="10" t="str">
+        <f ca="1" t="shared" ref="H23:H32" si="2">CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)</f>
+        <v>L8N2F8</v>
+      </c>
       <c r="I23" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" ht="57.6" spans="1:9">
+    <row r="24" ht="60" spans="1:9">
       <c r="A24" s="3" t="s">
         <v>95</v>
       </c>
@@ -2205,12 +2265,15 @@
       <c r="G24" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="10"/>
+      <c r="H24" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>L3U9S5</v>
+      </c>
       <c r="I24" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" ht="43.2" spans="1:9">
+    <row r="25" ht="45" spans="1:9">
       <c r="A25" s="3" t="s">
         <v>97</v>
       </c>
@@ -2232,12 +2295,15 @@
       <c r="G25" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="10"/>
+      <c r="H25" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>L1I0M9</v>
+      </c>
       <c r="I25" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="57.6" spans="1:9">
+    <row r="26" ht="60" spans="1:9">
       <c r="A26" s="3" t="s">
         <v>98</v>
       </c>
@@ -2259,12 +2325,15 @@
       <c r="G26" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H26" s="10"/>
+      <c r="H26" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>L5O8Z5</v>
+      </c>
       <c r="I26" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" ht="43.2" spans="1:9">
+    <row r="27" ht="45" spans="1:9">
       <c r="A27" s="3" t="s">
         <v>102</v>
       </c>
@@ -2286,12 +2355,15 @@
       <c r="G27" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="10"/>
+      <c r="H27" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>M1X1B5</v>
+      </c>
       <c r="I27" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="43.2" spans="1:9">
+    <row r="28" ht="45" spans="1:9">
       <c r="A28" s="3" t="s">
         <v>103</v>
       </c>
@@ -2313,12 +2385,15 @@
       <c r="G28" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H28" s="10"/>
+      <c r="H28" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>R1V4Y7</v>
+      </c>
       <c r="I28" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" ht="43.2" spans="1:9">
+    <row r="29" ht="45" spans="1:9">
       <c r="A29" s="3" t="s">
         <v>107</v>
       </c>
@@ -2340,12 +2415,15 @@
       <c r="G29" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H29" s="10"/>
+      <c r="H29" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>B9N5K8</v>
+      </c>
       <c r="I29" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="43.2" spans="1:9">
+    <row r="30" ht="45" spans="1:9">
       <c r="A30" s="3" t="s">
         <v>109</v>
       </c>
@@ -2367,12 +2445,15 @@
       <c r="G30" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H30" s="10"/>
+      <c r="H30" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>P7G3F4</v>
+      </c>
       <c r="I30" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" ht="57.6" spans="1:9">
+    <row r="31" ht="60" spans="1:9">
       <c r="A31" s="3" t="s">
         <v>111</v>
       </c>
@@ -2394,12 +2475,15 @@
       <c r="G31" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="H31" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>L6C5M1</v>
+      </c>
       <c r="I31" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="32" ht="43.2" spans="1:9">
+    <row r="32" ht="45" spans="1:9">
       <c r="A32" s="3" t="s">
         <v>115</v>
       </c>
@@ -2421,12 +2505,15 @@
       <c r="G32" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="10"/>
+      <c r="H32" s="10" t="str">
+        <f ca="1" t="shared" si="2"/>
+        <v>B6D6L0</v>
+      </c>
       <c r="I32" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" ht="43.2" spans="1:9">
+    <row r="33" ht="45" spans="1:9">
       <c r="A33" s="3" t="s">
         <v>118</v>
       </c>
@@ -2448,12 +2535,15 @@
       <c r="G33" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H33" s="10"/>
+      <c r="H33" s="10" t="str">
+        <f ca="1" t="shared" ref="H33:H42" si="3">CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)</f>
+        <v>A4J9M3</v>
+      </c>
       <c r="I33" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" ht="43.2" spans="1:9">
+    <row r="34" ht="45" spans="1:9">
       <c r="A34" s="3" t="s">
         <v>120</v>
       </c>
@@ -2475,12 +2565,15 @@
       <c r="G34" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="10"/>
+      <c r="H34" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>G7O3G7</v>
+      </c>
       <c r="I34" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" ht="43.2" spans="1:9">
+    <row r="35" ht="45" spans="1:9">
       <c r="A35" s="3" t="s">
         <v>122</v>
       </c>
@@ -2502,12 +2595,15 @@
       <c r="G35" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="10"/>
+      <c r="H35" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>B1B6M6</v>
+      </c>
       <c r="I35" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="43.2" spans="1:9">
+    <row r="36" ht="45" spans="1:9">
       <c r="A36" s="3" t="s">
         <v>125</v>
       </c>
@@ -2529,12 +2625,15 @@
       <c r="G36" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="H36" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>A8O1Y0</v>
+      </c>
       <c r="I36" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" ht="43.2" spans="1:9">
+    <row r="37" ht="45" spans="1:9">
       <c r="A37" s="3" t="s">
         <v>128</v>
       </c>
@@ -2556,12 +2655,15 @@
       <c r="G37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="10"/>
+      <c r="H37" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>L6O0Y9</v>
+      </c>
       <c r="I37" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" ht="43.2" spans="1:9">
+    <row r="38" ht="45" spans="1:9">
       <c r="A38" s="3" t="s">
         <v>130</v>
       </c>
@@ -2583,12 +2685,15 @@
       <c r="G38" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="H38" s="10"/>
+      <c r="H38" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>S4B5Y2</v>
+      </c>
       <c r="I38" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" ht="43.2" spans="1:9">
+    <row r="39" ht="45" spans="1:9">
       <c r="A39" s="3" t="s">
         <v>131</v>
       </c>
@@ -2610,12 +2715,15 @@
       <c r="G39" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="10"/>
+      <c r="H39" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>W6F0F6</v>
+      </c>
       <c r="I39" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" ht="43.2" spans="1:9">
+    <row r="40" ht="45" spans="1:9">
       <c r="A40" s="3" t="s">
         <v>134</v>
       </c>
@@ -2637,12 +2745,15 @@
       <c r="G40" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="H40" s="10"/>
+      <c r="H40" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>N9A6T5</v>
+      </c>
       <c r="I40" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" ht="43.2" spans="1:9">
+    <row r="41" ht="45" spans="1:9">
       <c r="A41" s="3" t="s">
         <v>136</v>
       </c>
@@ -2664,12 +2775,15 @@
       <c r="G41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="10"/>
+      <c r="H41" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>S8O4G0</v>
+      </c>
       <c r="I41" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" ht="43.2" spans="1:9">
+    <row r="42" ht="45" spans="1:9">
       <c r="A42" s="3" t="s">
         <v>139</v>
       </c>
@@ -2691,12 +2805,15 @@
       <c r="G42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="10"/>
+      <c r="H42" s="10" t="str">
+        <f ca="1" t="shared" si="3"/>
+        <v>B7X1Q8</v>
+      </c>
       <c r="I42" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" ht="43.2" spans="1:9">
+    <row r="43" ht="45" spans="1:9">
       <c r="A43" s="3" t="s">
         <v>140</v>
       </c>
@@ -2718,12 +2835,15 @@
       <c r="G43" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="10"/>
+      <c r="H43" s="10" t="str">
+        <f ca="1" t="shared" ref="H43:H51" si="4">CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)&amp;CHAR(RANDBETWEEN(65,90))&amp;RANDBETWEEN(0,9)</f>
+        <v>N9A1X3</v>
+      </c>
       <c r="I43" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="44" ht="43.2" spans="1:9">
+    <row r="44" ht="45" spans="1:9">
       <c r="A44" s="3" t="s">
         <v>141</v>
       </c>
@@ -2745,12 +2865,15 @@
       <c r="G44" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H44" s="10"/>
+      <c r="H44" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>O8Y5N1</v>
+      </c>
       <c r="I44" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="45" ht="43.2" spans="1:9">
+    <row r="45" ht="45" spans="1:9">
       <c r="A45" s="3" t="s">
         <v>144</v>
       </c>
@@ -2772,12 +2895,15 @@
       <c r="G45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H45" s="10"/>
+      <c r="H45" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>A8E5O3</v>
+      </c>
       <c r="I45" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" ht="43.2" spans="1:9">
+    <row r="46" ht="45" spans="1:9">
       <c r="A46" s="3" t="s">
         <v>145</v>
       </c>
@@ -2799,12 +2925,15 @@
       <c r="G46" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="10"/>
+      <c r="H46" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>C3N1W7</v>
+      </c>
       <c r="I46" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="47" ht="43.2" spans="1:9">
+    <row r="47" ht="45" spans="1:9">
       <c r="A47" s="3" t="s">
         <v>146</v>
       </c>
@@ -2826,12 +2955,15 @@
       <c r="G47" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H47" s="10"/>
+      <c r="H47" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>N8B4R2</v>
+      </c>
       <c r="I47" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" ht="57.6" spans="1:9">
+    <row r="48" ht="60" spans="1:9">
       <c r="A48" s="3" t="s">
         <v>147</v>
       </c>
@@ -2853,12 +2985,15 @@
       <c r="G48" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="10"/>
+      <c r="H48" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>P4Q1Q8</v>
+      </c>
       <c r="I48" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="49" ht="43.2" spans="1:9">
+    <row r="49" ht="45" spans="1:9">
       <c r="A49" s="3" t="s">
         <v>148</v>
       </c>
@@ -2880,12 +3015,15 @@
       <c r="G49" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H49" s="10"/>
+      <c r="H49" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>T9Q7B3</v>
+      </c>
       <c r="I49" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="50" ht="43.2" spans="1:9">
+    <row r="50" ht="45" spans="1:9">
       <c r="A50" s="3" t="s">
         <v>149</v>
       </c>
@@ -2907,12 +3045,15 @@
       <c r="G50" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H50" s="10"/>
+      <c r="H50" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>E0C2D6</v>
+      </c>
       <c r="I50" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="51" ht="43.2" spans="1:9">
+    <row r="51" ht="45" spans="1:9">
       <c r="A51" s="3" t="s">
         <v>150</v>
       </c>
@@ -2934,7 +3075,10 @@
       <c r="G51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H51" s="10"/>
+      <c r="H51" s="10" t="str">
+        <f ca="1" t="shared" si="4"/>
+        <v>V3H7B9</v>
+      </c>
       <c r="I51" s="11" t="s">
         <v>51</v>
       </c>
